--- a/examples/jcl.xlsx
+++ b/examples/jcl.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,16 +31,52 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F1F1F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,11 +84,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -61,6 +111,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -135,6 +194,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. A short name other rows refer to, e.g. design.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. A longer description.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. Months, most likely.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Shortest plausible duration, months.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Most likely duration, months.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Longest plausible duration, months.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. triangular (default), pert or uniform.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. IDs it waits for, separated by ;, each optionally with a link type and lag: design; fsw -4; bus SS +2.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Cost spent whatever the duration.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Lowest plausible fixed cost.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Most likely fixed cost.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Highest plausible fixed cost.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. triangular (default), pert or uniform.</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Cost per month the activity runs.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. What might happen.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The chance it happens: 0.3 or 30%.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The activity IDs it delays, separated by ;.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Shortest delay if it happens, months.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Most likely delay, months (or the only delay).</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Longest delay, months.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. triangular (default), pert or uniform.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Cost it adds besides the delay.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>The project's name, for the report.</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>What the costs are in.</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>Cost per month of the whole project running.</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>How much durations move together, 0 to 1.</t>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0">
+      <text>
+        <t>How much costs move together, 0 to 1.</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>The joint confidence to report: 0.7 for 70%.</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>How many simulations.</t>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Any whole number; the same seed gives the same answer.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,10 +662,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,325 +686,735 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Duration</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Duration Low</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Duration Most Likely</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Duration High</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Duration Distribution</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Predecessors</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Fixed Cost</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Cost Low</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Cost Most Likely</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Cost High</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Cost Distribution</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Burn Rate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>design</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Design through CDR</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>10.8</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="6" t="n">
         <v>16.8</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
+      <c r="G2" s="6" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="6" t="inlineStr"/>
+      <c r="K2" s="6" t="inlineStr"/>
+      <c r="L2" s="6" t="inlineStr"/>
+      <c r="M2" s="6" t="inlineStr"/>
+      <c r="N2" s="6" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>bus</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Spacecraft bus build</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="6" t="n">
         <v>25.2</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>design</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="M3" s="6" t="inlineStr"/>
+      <c r="N3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>instrument</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Instrument development</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>design</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="6" t="n">
         <v>28.5</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
+      <c r="M4" s="6" t="inlineStr"/>
+      <c r="N4" s="6" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>fsw</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Flight software</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>14.4</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>25.6</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>design -4</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr"/>
+      <c r="N5" s="6" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>i&amp;t</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Integration and test</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>7.2</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>14.4</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>bus; instrument; fsw</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr"/>
+      <c r="N6" s="6" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>launch</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Launch campaign</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>i&amp;t</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
+      <c r="N7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
+      <c r="N26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n"/>
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
+      <c r="N30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
+      <c r="N32" s="6" t="n"/>
+    </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="G2:G32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="stop">
+      <formula1>"triangular,pert,uniform"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="stop">
+      <formula1>"triangular,pert,uniform"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -778,107 +1428,364 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Activities</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Delay Low</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Delay Most Likely</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Delay High</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Delay Distribution</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Detector yield below plan</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>instrument</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
+      <c r="G2" s="6" t="inlineStr"/>
+      <c r="H2" s="6" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Thermal vacuum retest</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>i&amp;t</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
+      <c r="F3" s="6" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="G2:G28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="stop">
+      <formula1>"triangular,pert,uniform"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -890,125 +1797,132 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Example science mission</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>$M</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Standing Army</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Duration Correlation</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Cost Correlation</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Iterations</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="6" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Invented numbers, for illustration only: a small science spacecraft from design to launch, in months and $M.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="information">
+      <formula1>"dollars,thousands,millions,billions"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1016,84 +1930,151 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>How to fill in this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Yellow cells</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Yours to fill in. The example rows are there to show the layout: type over them, and add more rows in the yellow space below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Dark blue heading</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>A column that must be filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Light blue heading</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>An optional column: leave it blank if it doesn't apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Grey cells</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Labels: leave them as they are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Hover over a heading</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>A note says what goes in that column, in what units, with an example. A small arrow in a cell means a drop-down list of the allowed answers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Sheet or topic</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>What to put there</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>What this is</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>A project network with its uncertainty, for a joint cost and schedule (JCL) analysis: ce-core jcl --spec &lt;this file&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Activities sheet</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>One row per activity. ID is a short name the other rows refer to. Duration is in months; Duration Low, Most Likely and High are the range you believe (leave them blank for none). Predecessors lists the activities it waits for, separated by ;, each optionally with a link type and a lag in months: design; fsw -4; bus SS +2.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Costs</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Fixed Cost is spent whatever the duration, with Cost Low, Most Likely and High as its range. Burn Rate is spent per month the activity runs, so it grows when the activity slips.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Risks sheet</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Events that may happen. Probability is the chance (0.3 or 30%), Activities the IDs it delays (separated by ;), Delay the months it adds (one number, or Low, Most Likely and High), Cost what it adds besides the delay.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Settings sheet</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Standing Army is the cost per month of the whole project running. The correlations say how much durations, and costs, move together. Confidence is the joint level to report against (0.7 for 70%).</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Distribution columns</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Optional: triangular (the default), pert or uniform.</t>
         </is>
